--- a/coronavirus_response_forms/025_massage_salons_coronavirus_intake_form--coronavirus_response_forms.xlsx
+++ b/coronavirus_response_forms/025_massage_salons_coronavirus_intake_form--coronavirus_response_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'healthy',_'value':_'healthy'}</t>
+          <t>healthy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Healthy', 'value': 'Healthy'}</t>
+          <t>Healthy</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'not_healthy',_'value':_'not_healthy'}</t>
+          <t>not_healthy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Not Healthy', 'value': 'Not Healthy'}</t>
+          <t>Not Healthy</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'underlying_condition',_'value':_'underlying_condition'}</t>
+          <t>underlying_condition</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Underlying Condition', 'value': 'Underlying Condition'}</t>
+          <t>Underlying Condition</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'underlying_condition_with_a_fever',_'value':_'underlying_condition_with_a_fever'}</t>
+          <t>underlying_condition_with_a_fever</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Underlying Condition with a Fever', 'value': 'Underlying Condition with a Fever'}</t>
+          <t>Underlying Condition with a Fever</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'underlying_condition_with_fever_and_shortness_of_breath',_'value':_'underlying_condition_with_fever_and_shortness_of_breath'}</t>
+          <t>underlying_condition_with_fever_and_shortness_of_breath</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Underlying Condition with Fever and Shortness of Breath', 'value': 'Underlying Condition with Fever and Shortness of Breath'}</t>
+          <t>Underlying Condition with Fever and Shortness of Breath</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'underlying_condition_with_fever,_shortness_of_breath,_and_chest_pain',_'value':_'underlying_condition_with_fever,_shortness_of_breath,_and_chest_pain'}</t>
+          <t>underlying_condition_with_fever,_shortness_of_breath,_and_chest_pain</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Underlying Condition with Fever, Shortness of Breath, and Chest Pain', 'value': 'Underlying Condition with Fever, Shortness of Breath, and Chest Pain'}</t>
+          <t>Underlying Condition with Fever, Shortness of Breath, and Chest Pain</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'hospitalized_with_covid-19',_'value':_'hospitalized_with_covid-19'}</t>
+          <t>hospitalized_with_covid-19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Hospitalized with COVID-19', 'value': 'Hospitalized with COVID-19'}</t>
+          <t>Hospitalized with COVID-19</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'not_vaccinated',_'value':_'not_vaccinated'}</t>
+          <t>not_vaccinated</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Not Vaccinated', 'value': 'Not Vaccinated'}</t>
+          <t>Not Vaccinated</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'partially_vaccinated',_'value':_'partially_vaccinated'}</t>
+          <t>partially_vaccinated</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Partially Vaccinated', 'value': 'Partially Vaccinated'}</t>
+          <t>Partially Vaccinated</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'fully_vaccinated',_'value':_'fully_vaccinated'}</t>
+          <t>fully_vaccinated</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Fully Vaccinated', 'value': 'Fully Vaccinated'}</t>
+          <t>Fully Vaccinated</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'vaccinated_and_boosted',_'value':_'vaccinated_and_boosted'}</t>
+          <t>vaccinated_and_boosted</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'Vaccinated and Boosted', 'value': 'Vaccinated and Boosted'}</t>
+          <t>Vaccinated and Boosted</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'positive',_'value':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'Positive', 'value': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'negative',_'value':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'Negative', 'value': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'unknown',_'value':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'Unknown', 'value': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'not_scheduled',_'value':_'not_scheduled'}</t>
+          <t>not_scheduled</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'Not Scheduled', 'value': 'Not Scheduled'}</t>
+          <t>Not Scheduled</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_'scheduled',_'value':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 'Scheduled', 'value': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'name':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'name': 'Completed', 'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
